--- a/proyecto-reto/04-fabricacion/hojas-viajeras/OF-2026-BRZ-001_hoja-viajera.xlsx
+++ b/proyecto-reto/04-fabricacion/hojas-viajeras/OF-2026-BRZ-001_hoja-viajera.xlsx
@@ -457,6 +457,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -530,6 +532,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -682,6 +685,7 @@
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -690,7 +694,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Registro posterior: maquinado la semana del 2026-10-05 al 2026-10-10 (fechas aproximadas). Material: OC-2026-009.</t>
+          <t>Registro posterior: maquinado la semana del 2026-10-05 al 2026-10-10 (fechas aproximadas). Material: OC-2026-010 (Metales MarChina).</t>
         </is>
       </c>
     </row>

--- a/proyecto-reto/04-fabricacion/hojas-viajeras/OF-2026-BRZ-001_hoja-viajera.xlsx
+++ b/proyecto-reto/04-fabricacion/hojas-viajeras/OF-2026-BRZ-001_hoja-viajera.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -457,8 +457,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -484,7 +482,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -506,7 +504,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -532,7 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -594,8 +591,16 @@
           <t>Surtir tramo de solera 6061-T6 y verificar el bruto exacto (el cero G54 va en su esquina)</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Osmar</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
@@ -615,7 +620,11 @@
           <t>Programa O01001, bruto 152.4 x 400 x 6.35 mm, herramientas T7 T2 T1 T6 T5 T4. Barrenos con G83 (picoteo 2 mm), luego bolsa y contorno. Refrigerante M08</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Osmar</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr"/>
@@ -636,9 +645,17 @@
           <t>Desprender la pieza por la piel de 0.3 mm y desbarbar</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Osmar</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -657,7 +674,11 @@
           <t>Verificar contorno, barrenos y bolsa contra plano</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
@@ -678,7 +699,11 @@
           <t>Firma de calidad y entrega al ensamble del brazo</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
@@ -694,10 +719,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Registro posterior: maquinado la semana del 2026-10-05 al 2026-10-10 (fechas aproximadas). Material: OC-2026-010 (Metales MarChina).</t>
-        </is>
-      </c>
-    </row>
+          <t>Maquinado por Osmar del 2026-09-30 al 2026-10-07 (fechas confirmadas por Rodrigo el 2026-10-10). Material: OC-2026-010 (Metales MarChina). PENDIENTE: inspeccion dimensional (op 40), conteo de buenas/scrap y firma de calidad (Rodrigo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
